--- a/陕西煤业/财务指标_陕西煤业.xlsx
+++ b/陕西煤业/财务指标_陕西煤业.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="105" windowWidth="12765" windowHeight="5715" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="105" windowWidth="12765" windowHeight="5715" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="折旧对比" sheetId="13" r:id="rId1"/>
@@ -20221,7 +20221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="681">
   <si>
     <t>总资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -21594,10 +21594,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>以摊余成本计量的金融
 资产终止确认收益</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -21623,50 +21619,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>境内法人持股</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  16.55%  -&gt;  16.55%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>高管股份</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.6%   -&gt;  0.57%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>应收利息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -21821,65 +21773,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>生产量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  63787.61(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>茅台酒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>42,828.59 +</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>系列酒</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">20,959.02) </t>
-    </r>
-  </si>
-  <si>
-    <t>同上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>营业收入</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -21927,267 +21820,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>有限售条件股份  0.13% -&gt; 0.03%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>公司有限售条件股份均为高管锁定股份。报告期内，因谢明先生、张良先生、蔡秋全先生、郭智勇先生、孙跃先生、敖
-治平先生、曾颖先生离职半年后全部股份解锁，以及董事长刘淼先生、董事、副总经理沈才洪先生的股份年度解锁，致使有
-限售条件股份减少</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1,309,922</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>股，无限售条件股份相应增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1,309,922</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>股。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  26.61%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  23.67%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  4.01%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中国证券金融股份有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  2.91%
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 26.61% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  23.67% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  4.01% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1</t>
     </r>
@@ -23049,31 +22681,6 @@
       <t xml:space="preserve">日止，协议的签署有利于国有股东进一步完善和明晰股权关系，规范法人治理结构。协议签署后，公司股权结构未发生变化，公司控股股东仍为泸州老窖集团有限责任公司，实际控制人仍为泸州市国资委。
 </t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司正式员工总数为1622人
-(0.86-0.85+2.3) / 1622  人均薪酬14.2万
-董事、监事和高级管理人员持股减少307,500(离任)
-2015年06月30日董事长从谢明到刘淼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限售条件股份  99.87% -&gt; 99.97%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限售条件股份  99.97% -&gt; 99.97%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司正式员工总数为2009人
-(1.3-0.86+2.8) / 2009  人均薪酬16.1万</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司正式员工总数为2451人
-(1.38-1.3+4) / 2451  人均薪酬16.6万</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -23643,268 +23250,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>有限售条件股份  0.03% -&gt; 0.03%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">股票及其衍生证券名称  非公开发行股票
-发行日期  2017年08月10
-发行价格（或利率） 48元
-发行数量  62,500,000
-上市日期  2017 年 09 月 14
-获准上市交易数量  62,500,000
-核准公司非公开发行不超过149,253,731股新股。公司以询价方式确定最终发行价格为48元/股，募集资金总额人民币
-30亿元，扣除承销费用 0.47亿（含税）和验资费30万元（含税），实际募集的资金人民币29.53亿，加上承销费用和验资费用可抵扣的增值税进项税268万，募集资金净额为29.55亿元。本次非公开发行的62,500,000股人民币普通股于2017年9月14日在深交所上市。公司总股本由本次非公开发行前的1,402,252,476股增加至1,464,752,476股。
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">限售股份变动情况
-泸州酒业投资有限公司  4,166,666  非公开发行新股
-易方达基金管理有限公司  21,874,999  非公开发行新股
-汇添富基金管股份有限公司  6,666,666 非公开发行新股
-博时基金管理有限公司  9,583,333  非公开发行新股
-平安资产管理有限责任公司  6,666,666  非公开发行新股
-财通基金管理有限公司  7,083,333  非公开发行新股
-民生加银基金管理有限公司  6,458,337  非公开发行新股
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  28.11%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  26.1%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中国证券金融股份有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.77%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中央汇金资产管理有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.49%
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 28.11% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  26.1% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-实际控制人泸州市国有资产监督管理委员会占用股份与上期一致，占比</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>54.29%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1</t>
     </r>
@@ -24730,370 +24075,6 @@
       <t xml:space="preserve">万元
 </t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有限售条件股份  0.03% -&gt; 4.3%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限售条件股份  99.97% -&gt; 95.7%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限售条件股份  95.7% -&gt; 99.68%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>限售股份变动情况
-泸州酒业投资有限公司  4,166,666  非公开发行新股
-易方达基金管理有限公司  0  非公开发行新股
-汇添富基金管股份有限公司  0 非公开发行新股
-博时基金管理有限公司  0  非公开发行新股
-平安资产管理有限责任公司  0  非公开发行新股
-财通基金管理有限公司  0  非公开发行新股
-民生加银基金管理有限公司  0  非公开发行新股</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  26.02%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  24.99%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中国证券金融股份有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.74%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>香港中央结算有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.62%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中央汇金资产管理有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.43%
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 26.02% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>四川金舵投资有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">0.38% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  24.99% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-实际控制人泸州市国有资产监督管理委员会占用股份与上期不一致，占比从</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>54.29%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>减少到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>51.47%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司正式员工总数为2880人
-(2.7-1.38+5.7) / 2880  人均薪酬24.4万</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -25935,567 +24916,6 @@
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有限售条件股份  4.3% -&gt; 0.32%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有限售条件股份  0.32% -&gt; 0.32%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无限售条件股份  99.68% -&gt; 99.68%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2019年8月28日，公司2019年面向合格投资者公开发行公司债券（第一期）发行完毕，发行价格为人民币 100 元/张，
-最终实际发行规模为25亿元，最终票面利率为3.58%，并于2019年9月4日在深交所上市交易。
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  26.02%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  24.99%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中国证券金融股份有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  2.31%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>香港中央结算有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  3.27%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>易方达消费行业股票型证券投资基金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.69%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中央汇金资产管理有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.43%
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 26.02% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  24.99% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-实际控制人泸州市国有资产监督管理委员会占用股份与上期不一致，占比从</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>51.47%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>减少到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>51.09%</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  26.02%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  24.99%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中国证券金融股份有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  2.31%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>香港中央结算有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  2.75%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>易方达消费行业股票型证券投资基金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.46%
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中央汇金资产管理有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  1.43%
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖集团有限责任公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 26.02% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 100% -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州市兴泸投资集团有限公司</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  24.99% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>泸州老窖股份有限公司
-泸州市国有资产监督管理委员会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  0.08% -&gt;  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">泸州老窖股份有限公司
-</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司正式员工总数为3228人
-(3.4-2.7+7.65) / 3228  人均薪酬25.9万
-董事、副总经理沈才洪减持46,125股</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -33466,60 +31886,6 @@
         <charset val="134"/>
       </rPr>
       <t>亿</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">公司正式员工总数为人
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(13.7-11.7+67.2) / 36344</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>人均薪酬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>万</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -36989,11 +35355,1250 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、陕西煤业化工集团有限责任公司</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  63.14%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>香港中央结算有限公司</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  3.05%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕西煤业股份有限公司回购专用证券账户</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  3.05%
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、陕西省国有资产监督管理委员会</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 100% -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕西煤业化工集团有限责任公司陕西煤业化工集团有限责任公司</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 63.14% -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">陕西煤业股份有限公司
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有限售条件股份</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  0% -&gt; 0%</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公司正式员工总数为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>36344</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">人
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(13.7-11.7+67.2) / 36344</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人均薪酬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>公司正式员工总数为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>36344</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">人
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(13.7-11.7+67.2) / 36344</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人均薪酬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">万
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2020</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日董事长从闵龙（退休）到杨照乾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、公司于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2017 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 9-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日面向合格投资者公开发行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2017 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年度公司债券（第一期），债券简称</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">“17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕煤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 01”,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发行规模为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元，票面利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 4.75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，债券期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年，该期债券无担保
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年公司面向合格投资者公开发行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年度公司债券（第一期），债券简称“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕煤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”，发行规模</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元，票面利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 4.86%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，债券期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，该期债券无担保</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、公司于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2017 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 9-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日面向合格投资者公开发行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2017 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年度公司债券（第一期），债券简称“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕煤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发行规模为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元，票面利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 4.75%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，债券期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年，该期债券无担保
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年公司面向合格投资者公开发行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年度公司债券（第一期），债券简称“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕煤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”，发行规模</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿元，票面利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 4.86%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，债券期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，该期债券无担保
+截至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">“17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕煤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 01”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">“18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陕煤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 01”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">募集资金扣除发行费用后全部用于偿还金融机构贷款，与募集说明书承诺的募集资金用途、使用计划及其他约定一致。
+截止报告期末无欠本息情况
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="15">
     <font>
       <sz val="11"/>
@@ -37410,13 +37015,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -37425,13 +37030,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -37439,7 +37038,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -37448,14 +37053,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -37463,11 +37068,16 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -37541,6 +37151,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -37575,6 +37186,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -37750,7 +37362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -37760,10 +37372,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" s="15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="142.5">
@@ -37771,10 +37383,10 @@
         <v>2012</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -37834,8 +37446,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A3:F20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:F21"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22.25" customWidth="1"/>
@@ -37866,7 +37478,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="111">
+      <c r="A5" s="120">
         <v>2012</v>
       </c>
       <c r="B5" s="4"/>
@@ -37874,7 +37486,7 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="111"/>
+      <c r="A6" s="120"/>
       <c r="B6" s="13"/>
       <c r="C6" s="50"/>
       <c r="D6" s="4"/>
@@ -37882,7 +37494,7 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="111">
+      <c r="A7" s="120">
         <v>2013</v>
       </c>
       <c r="B7" s="1"/>
@@ -37890,7 +37502,7 @@
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="111"/>
+      <c r="A8" s="120"/>
       <c r="B8" s="4"/>
       <c r="C8" s="37"/>
       <c r="D8" s="4"/>
@@ -37898,164 +37510,116 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A9" s="111">
+      <c r="A9" s="120">
         <v>2014</v>
       </c>
       <c r="B9" s="1"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="113"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="121"/>
     </row>
     <row r="10" spans="1:6" ht="141.75" customHeight="1">
-      <c r="A10" s="111"/>
+      <c r="A10" s="120"/>
       <c r="B10" s="5"/>
       <c r="C10" s="41"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="121"/>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A11" s="111">
+      <c r="A11" s="120">
         <v>2015</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D11" s="106"/>
-      <c r="E11" s="112" t="s">
-        <v>289</v>
-      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="119"/>
     </row>
     <row r="12" spans="1:6" ht="163.5" customHeight="1">
-      <c r="A12" s="111"/>
-      <c r="B12" s="5" t="s">
-        <v>288</v>
-      </c>
+      <c r="A12" s="120"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="112"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="119"/>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A13" s="116">
+      <c r="A13" s="111">
         <v>2016</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C13" s="114" t="s">
-        <v>293</v>
-      </c>
-      <c r="D13" s="119" t="s">
-        <v>238</v>
-      </c>
-      <c r="E13" s="112" t="s">
-        <v>300</v>
-      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="119"/>
     </row>
     <row r="14" spans="1:6" ht="219" customHeight="1">
-      <c r="A14" s="116"/>
+      <c r="A14" s="111"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="115"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="113"/>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A15" s="116">
+      <c r="A15" s="111">
         <v>2017</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C15" s="114" t="s">
-        <v>304</v>
-      </c>
-      <c r="D15" s="114" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="117" t="s">
-        <v>307</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="117"/>
     </row>
     <row r="16" spans="1:6" ht="222.75" customHeight="1">
-      <c r="A16" s="116"/>
-      <c r="B16" s="91" t="s">
-        <v>299</v>
-      </c>
-      <c r="C16" s="114"/>
-      <c r="D16" s="115"/>
+      <c r="A16" s="111"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="113"/>
       <c r="E16" s="118"/>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A17" s="116">
+      <c r="A17" s="111">
         <v>2018</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C17" s="114" t="s">
-        <v>305</v>
-      </c>
-      <c r="D17" s="119" t="s">
-        <v>279</v>
-      </c>
-      <c r="E17" s="117" t="s">
-        <v>322</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="117"/>
     </row>
     <row r="18" spans="1:5" ht="225" customHeight="1">
-      <c r="A18" s="116"/>
-      <c r="B18" s="91" t="s">
-        <v>306</v>
-      </c>
-      <c r="C18" s="114"/>
-      <c r="D18" s="116"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="111"/>
       <c r="E18" s="118"/>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A19" s="116">
+      <c r="A19" s="111">
         <v>2019</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C19" s="114" t="s">
-        <v>320</v>
-      </c>
-      <c r="D19" s="114" t="s">
-        <v>321</v>
-      </c>
-      <c r="E19" s="120" t="s">
-        <v>323</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="114"/>
     </row>
     <row r="20" spans="1:5" ht="184.5" customHeight="1">
-      <c r="A20" s="116"/>
-      <c r="B20" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C20" s="114"/>
-      <c r="D20" s="115"/>
-      <c r="E20" s="121"/>
+      <c r="A20" s="111"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="115"/>
+    </row>
+    <row r="21" spans="1:5" ht="99">
+      <c r="A21" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>675</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:E14"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="E11:E12"/>
@@ -38065,6 +37629,22 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38074,8 +37654,8 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -38104,44 +37684,42 @@
       </c>
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:2" ht="81.75">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>2015</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>291</v>
-      </c>
+      <c r="B5" s="4"/>
     </row>
-    <row r="6" spans="1:2" ht="27.75">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>2016</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>294</v>
-      </c>
+      <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:2" ht="41.25">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>2017</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>295</v>
-      </c>
+      <c r="B7" s="22"/>
     </row>
-    <row r="8" spans="1:2" ht="27.75">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>2018</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>308</v>
-      </c>
+      <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:2" ht="41.25">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>2019</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>324</v>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:2" ht="56.25">
+      <c r="A10">
+        <v>2020</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -38151,7 +37729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -38163,7 +37741,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>226</v>
@@ -38175,7 +37753,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -38231,22 +37809,22 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -38254,19 +37832,19 @@
         <v>2019</v>
       </c>
       <c r="B15" t="s">
-        <v>556</v>
+        <v>527</v>
       </c>
       <c r="C15" t="s">
-        <v>553</v>
+        <v>524</v>
       </c>
       <c r="D15" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="E15" t="s">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="F15" t="s">
-        <v>663</v>
+        <v>634</v>
       </c>
       <c r="G15">
         <v>0.2127</v>
@@ -38274,46 +37852,46 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="B16" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="C16" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="B17" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="C17" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="B18" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="C18" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="C19" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -38321,19 +37899,19 @@
         <v>2020</v>
       </c>
       <c r="B21" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="C21" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="D21" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="E21" t="s">
-        <v>674</v>
+        <v>645</v>
       </c>
       <c r="F21" t="s">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="G21">
         <v>0.23180000000000001</v>
@@ -38341,46 +37919,46 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="B22" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="C22" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="B23" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="C23" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="B24" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="C24" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="B25" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="C25" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -38392,7 +37970,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BS12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -38434,28 +38012,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>691</v>
+        <v>661</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>7</v>
@@ -38473,22 +38051,22 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>692</v>
+        <v>662</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>10</v>
@@ -38503,7 +38081,7 @@
         <v>13</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>14</v>
@@ -38527,7 +38105,7 @@
         <v>82</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AK1" s="1" t="s">
         <v>19</v>
@@ -38539,7 +38117,7 @@
         <v>21</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>22</v>
@@ -38557,10 +38135,10 @@
         <v>25</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="AV1" s="1" t="s">
         <v>26</v>
@@ -38569,16 +38147,16 @@
         <v>27</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="AZ1" s="1" t="s">
         <v>90</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="BC1" s="1" t="s">
         <v>87</v>
@@ -38608,16 +38186,16 @@
         <v>88</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="BN1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="BQ1" s="1" t="s">
         <v>36</v>
@@ -38744,155 +38322,155 @@
         <v>2019</v>
       </c>
       <c r="B11" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="D11" s="98" t="s">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="F11" s="45" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="G11" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="I11" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="K11" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="L11" s="45" t="s">
-        <v>668</v>
+        <v>639</v>
       </c>
       <c r="N11" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="O11" t="s">
-        <v>647</v>
+        <v>618</v>
       </c>
       <c r="R11" s="45"/>
       <c r="S11" s="45" t="s">
-        <v>584</v>
+        <v>555</v>
       </c>
       <c r="U11" t="s">
-        <v>588</v>
+        <v>559</v>
       </c>
       <c r="W11" t="s">
-        <v>671</v>
+        <v>642</v>
       </c>
       <c r="X11" t="s">
+        <v>339</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>341</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>344</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>346</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>348</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>350</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>352</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>354</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>355</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>360</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>358</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>362</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>366</v>
+      </c>
+      <c r="AP11" t="s">
         <v>368</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AS11" s="45" t="s">
         <v>370</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AT11" s="45" t="s">
         <v>373</v>
       </c>
-      <c r="AC11" t="s">
-        <v>375</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>377</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>379</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>381</v>
-      </c>
-      <c r="AG11" t="s">
+      <c r="AU11" s="45" t="s">
+        <v>376</v>
+      </c>
+      <c r="AV11" s="45" t="s">
+        <v>530</v>
+      </c>
+      <c r="AX11" s="45" t="s">
+        <v>533</v>
+      </c>
+      <c r="AY11" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="AZ11" s="45" t="s">
+        <v>380</v>
+      </c>
+      <c r="BB11" s="45" t="s">
         <v>383</v>
       </c>
-      <c r="AI11" t="s">
-        <v>384</v>
-      </c>
-      <c r="AK11" t="s">
+      <c r="BC11" s="45" t="s">
+        <v>385</v>
+      </c>
+      <c r="BD11" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="BE11" s="45" t="s">
         <v>389</v>
       </c>
-      <c r="AL11" t="s">
-        <v>387</v>
-      </c>
-      <c r="AM11" t="s">
+      <c r="BF11" s="45" t="s">
         <v>391</v>
       </c>
-      <c r="AO11" t="s">
-        <v>395</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>397</v>
-      </c>
-      <c r="AS11" s="45" t="s">
-        <v>399</v>
-      </c>
-      <c r="AT11" s="45" t="s">
+      <c r="BG11" s="45" t="s">
+        <v>392</v>
+      </c>
+      <c r="BI11" s="88" t="s">
+        <v>394</v>
+      </c>
+      <c r="BJ11" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="BK11" s="45" t="s">
+        <v>398</v>
+      </c>
+      <c r="BL11" s="40" t="s">
+        <v>400</v>
+      </c>
+      <c r="BM11" s="45" t="s">
         <v>402</v>
       </c>
-      <c r="AU11" s="45" t="s">
-        <v>405</v>
-      </c>
-      <c r="AV11" s="45" t="s">
-        <v>559</v>
-      </c>
-      <c r="AX11" s="45" t="s">
-        <v>562</v>
-      </c>
-      <c r="AY11" s="45" t="s">
-        <v>407</v>
-      </c>
-      <c r="AZ11" s="45" t="s">
-        <v>409</v>
-      </c>
-      <c r="BB11" s="45" t="s">
-        <v>412</v>
-      </c>
-      <c r="BC11" s="45" t="s">
-        <v>414</v>
-      </c>
-      <c r="BD11" s="45" t="s">
-        <v>416</v>
-      </c>
-      <c r="BE11" s="45" t="s">
-        <v>418</v>
-      </c>
-      <c r="BF11" s="45" t="s">
-        <v>420</v>
-      </c>
-      <c r="BG11" s="45" t="s">
-        <v>421</v>
-      </c>
-      <c r="BI11" s="88" t="s">
-        <v>423</v>
-      </c>
-      <c r="BJ11" s="45" t="s">
-        <v>425</v>
-      </c>
-      <c r="BK11" s="45" t="s">
-        <v>427</v>
-      </c>
-      <c r="BL11" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="BM11" s="45" t="s">
-        <v>431</v>
-      </c>
       <c r="BN11" s="45" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="BP11" s="45" t="s">
-        <v>433</v>
+        <v>404</v>
       </c>
       <c r="BQ11" s="45" t="s">
-        <v>435</v>
+        <v>406</v>
       </c>
       <c r="BR11" s="45" t="s">
-        <v>437</v>
+        <v>408</v>
       </c>
       <c r="BS11" s="45" t="s">
-        <v>439</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:71">
@@ -38900,160 +38478,160 @@
         <v>2020</v>
       </c>
       <c r="B12" t="s">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="D12" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="F12" t="s">
+        <v>328</v>
+      </c>
+      <c r="G12" t="s">
+        <v>326</v>
+      </c>
+      <c r="H12" t="s">
+        <v>501</v>
+      </c>
+      <c r="I12" t="s">
+        <v>330</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="L12" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="N12" t="s">
+        <v>333</v>
+      </c>
+      <c r="O12" t="s">
+        <v>335</v>
+      </c>
+      <c r="S12" t="s">
+        <v>336</v>
+      </c>
+      <c r="U12" t="s">
+        <v>557</v>
+      </c>
+      <c r="W12" t="s">
+        <v>337</v>
+      </c>
+      <c r="X12" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>343</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>345</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>347</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>349</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>351</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>353</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>356</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>359</v>
+      </c>
+      <c r="AL12" t="s">
         <v>357</v>
       </c>
-      <c r="G12" t="s">
-        <v>355</v>
-      </c>
-      <c r="H12" t="s">
-        <v>530</v>
-      </c>
-      <c r="I12" t="s">
-        <v>359</v>
-      </c>
-      <c r="K12" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="L12" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="N12" t="s">
-        <v>362</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="AM12" t="s">
+        <v>361</v>
+      </c>
+      <c r="AN12" t="s">
         <v>364</v>
       </c>
-      <c r="S12" t="s">
+      <c r="AO12" t="s">
         <v>365</v>
       </c>
-      <c r="U12" t="s">
-        <v>586</v>
-      </c>
-      <c r="W12" t="s">
-        <v>366</v>
-      </c>
-      <c r="X12" t="s">
+      <c r="AP12" t="s">
         <v>367</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AS12" t="s">
         <v>369</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AT12" t="s">
         <v>372</v>
       </c>
-      <c r="AC12" t="s">
-        <v>374</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>376</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>378</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>380</v>
-      </c>
-      <c r="AG12" t="s">
+      <c r="AU12" t="s">
+        <v>375</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>529</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>377</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>361</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>379</v>
+      </c>
+      <c r="BB12" t="s">
         <v>382</v>
       </c>
-      <c r="AI12" t="s">
-        <v>385</v>
-      </c>
-      <c r="AK12" t="s">
+      <c r="BC12" t="s">
+        <v>384</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>386</v>
+      </c>
+      <c r="BE12" t="s">
         <v>388</v>
       </c>
-      <c r="AL12" t="s">
-        <v>386</v>
-      </c>
-      <c r="AM12" t="s">
+      <c r="BF12" t="s">
         <v>390</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="BG12" t="s">
+        <v>623</v>
+      </c>
+      <c r="BI12" t="s">
         <v>393</v>
       </c>
-      <c r="AO12" t="s">
-        <v>394</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>396</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>398</v>
-      </c>
-      <c r="AT12" t="s">
+      <c r="BJ12" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>397</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>399</v>
+      </c>
+      <c r="BM12" t="s">
         <v>401</v>
       </c>
-      <c r="AU12" t="s">
-        <v>404</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>558</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>406</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>390</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>408</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>411</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>413</v>
-      </c>
-      <c r="BD12" t="s">
-        <v>415</v>
-      </c>
-      <c r="BE12" t="s">
-        <v>417</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>419</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>652</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>422</v>
-      </c>
-      <c r="BJ12" t="s">
-        <v>424</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>426</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>428</v>
-      </c>
-      <c r="BM12" t="s">
-        <v>430</v>
-      </c>
       <c r="BN12" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="BP12" t="s">
-        <v>432</v>
+        <v>403</v>
       </c>
       <c r="BQ12" t="s">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="BR12" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="BS12" t="s">
-        <v>438</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -39065,7 +38643,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -39091,10 +38669,10 @@
         <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>38</v>
@@ -39103,10 +38681,10 @@
         <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
@@ -39118,7 +38696,7 @@
         <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>44</v>
@@ -39136,19 +38714,19 @@
         <v>48</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>49</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>95</v>
@@ -39181,7 +38759,7 @@
         <v>79</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:37">
@@ -39256,73 +38834,73 @@
         <v>2019</v>
       </c>
       <c r="B11" t="s">
-        <v>670</v>
+        <v>641</v>
       </c>
       <c r="E11" t="s">
-        <v>604</v>
+        <v>575</v>
       </c>
       <c r="G11" s="45" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="J11" s="45" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="K11" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="L11" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="M11" t="s">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="N11" s="70" t="s">
-        <v>537</v>
+        <v>508</v>
       </c>
       <c r="P11" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="R11" t="s">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="S11" t="s">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="W11" t="s">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="X11" t="s">
-        <v>611</v>
+        <v>582</v>
       </c>
       <c r="Y11" s="70" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="Z11" t="s">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="AA11" t="s">
-        <v>660</v>
+        <v>631</v>
       </c>
       <c r="AC11" t="s">
-        <v>460</v>
+        <v>431</v>
       </c>
       <c r="AD11" s="45" t="s">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="AE11" t="s">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="AG11" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="AH11" t="s">
-        <v>619</v>
+        <v>590</v>
       </c>
       <c r="AI11" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="AJ11" t="s">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="AK11" s="46">
         <v>0.3</v>
@@ -39333,73 +38911,73 @@
         <v>2020</v>
       </c>
       <c r="B12" t="s">
-        <v>665</v>
+        <v>636</v>
       </c>
       <c r="E12" t="s">
-        <v>603</v>
+        <v>574</v>
       </c>
       <c r="G12" t="s">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="L12" t="s">
-        <v>607</v>
+        <v>578</v>
       </c>
       <c r="M12" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="N12" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="P12" t="s">
-        <v>456</v>
+        <v>427</v>
       </c>
       <c r="R12" t="s">
-        <v>450</v>
+        <v>421</v>
       </c>
       <c r="S12" t="s">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="W12" t="s">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="X12" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="Y12" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="Z12" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="AA12" t="s">
-        <v>659</v>
+        <v>630</v>
       </c>
       <c r="AC12" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="AD12" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="AE12" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="AG12" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="AH12" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="AI12" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
       <c r="AJ12" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="AK12" s="2">
         <v>0.52149999999999996</v>
@@ -39414,7 +38992,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AS12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -39448,13 +39026,13 @@
   <sheetData>
     <row r="1" spans="1:45" ht="69">
       <c r="B1" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>91</v>
@@ -39469,16 +39047,16 @@
         <v>58</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>59</v>
@@ -39514,7 +39092,7 @@
         <v>66</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AB1" s="5" t="s">
         <v>69</v>
@@ -39523,7 +39101,7 @@
         <v>70</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>73</v>
@@ -39538,7 +39116,7 @@
         <v>92</v>
       </c>
       <c r="AJ1" s="4" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="AK1" s="4" t="s">
         <v>93</v>
@@ -39550,7 +39128,7 @@
         <v>75</v>
       </c>
       <c r="AO1" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AP1" s="4" t="s">
         <v>94</v>
@@ -39640,97 +39218,97 @@
         <v>2019</v>
       </c>
       <c r="B11" t="s">
+        <v>441</v>
+      </c>
+      <c r="E11" t="s">
+        <v>443</v>
+      </c>
+      <c r="F11" t="s">
+        <v>445</v>
+      </c>
+      <c r="G11" t="s">
+        <v>447</v>
+      </c>
+      <c r="I11" s="45" t="s">
+        <v>449</v>
+      </c>
+      <c r="N11" t="s">
+        <v>450</v>
+      </c>
+      <c r="O11" t="s">
+        <v>452</v>
+      </c>
+      <c r="P11" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>456</v>
+      </c>
+      <c r="R11" s="45" t="s">
+        <v>589</v>
+      </c>
+      <c r="T11" t="s">
+        <v>458</v>
+      </c>
+      <c r="U11" t="s">
+        <v>459</v>
+      </c>
+      <c r="V11" t="s">
+        <v>608</v>
+      </c>
+      <c r="X11" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>466</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>468</v>
+      </c>
+      <c r="AC11" t="s">
         <v>470</v>
       </c>
-      <c r="E11" t="s">
+      <c r="AD11" t="s">
         <v>472</v>
       </c>
-      <c r="F11" t="s">
+      <c r="AE11" t="s">
         <v>474</v>
       </c>
-      <c r="G11" t="s">
-        <v>476</v>
-      </c>
-      <c r="I11" s="45" t="s">
-        <v>478</v>
-      </c>
-      <c r="N11" t="s">
-        <v>479</v>
-      </c>
-      <c r="O11" t="s">
-        <v>481</v>
-      </c>
-      <c r="P11" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>485</v>
-      </c>
-      <c r="R11" s="45" t="s">
-        <v>618</v>
-      </c>
-      <c r="T11" t="s">
-        <v>487</v>
-      </c>
-      <c r="U11" t="s">
+      <c r="AF11" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>477</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>610</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>480</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>482</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>484</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>486</v>
+      </c>
+      <c r="AP11" s="45" t="s">
         <v>488</v>
       </c>
-      <c r="V11" t="s">
-        <v>637</v>
-      </c>
-      <c r="X11" t="s">
-        <v>491</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>493</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>495</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>497</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>499</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>501</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>503</v>
-      </c>
-      <c r="AF11" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>506</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>639</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>509</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>511</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>513</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>515</v>
-      </c>
-      <c r="AP11" s="45" t="s">
-        <v>517</v>
-      </c>
       <c r="AQ11" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="AR11" s="1" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
       <c r="AS11" t="s">
-        <v>626</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" spans="1:45">
@@ -39738,97 +39316,97 @@
         <v>2020</v>
       </c>
       <c r="B12" t="s">
-        <v>623</v>
+        <v>594</v>
       </c>
       <c r="E12" t="s">
+        <v>442</v>
+      </c>
+      <c r="F12" t="s">
+        <v>444</v>
+      </c>
+      <c r="G12" t="s">
+        <v>446</v>
+      </c>
+      <c r="I12" t="s">
+        <v>448</v>
+      </c>
+      <c r="N12" t="s">
+        <v>648</v>
+      </c>
+      <c r="O12" t="s">
+        <v>451</v>
+      </c>
+      <c r="P12" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>455</v>
+      </c>
+      <c r="R12" t="s">
+        <v>457</v>
+      </c>
+      <c r="T12" s="31" t="s">
+        <v>656</v>
+      </c>
+      <c r="U12" s="31" t="s">
+        <v>657</v>
+      </c>
+      <c r="V12" t="s">
+        <v>460</v>
+      </c>
+      <c r="X12" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>463</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>465</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>467</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>469</v>
+      </c>
+      <c r="AD12" t="s">
         <v>471</v>
       </c>
-      <c r="F12" t="s">
+      <c r="AE12" t="s">
         <v>473</v>
       </c>
-      <c r="G12" t="s">
-        <v>475</v>
-      </c>
-      <c r="I12" t="s">
-        <v>477</v>
-      </c>
-      <c r="N12" t="s">
-        <v>677</v>
-      </c>
-      <c r="O12" t="s">
-        <v>480</v>
-      </c>
-      <c r="P12" t="s">
-        <v>482</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>484</v>
-      </c>
-      <c r="R12" t="s">
-        <v>486</v>
-      </c>
-      <c r="T12" s="31" t="s">
-        <v>686</v>
-      </c>
-      <c r="U12" s="31" t="s">
-        <v>687</v>
-      </c>
-      <c r="V12" t="s">
+      <c r="AF12" t="s">
+        <v>600</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>476</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>478</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>479</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>481</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>483</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>485</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>487</v>
+      </c>
+      <c r="AQ12" t="s">
         <v>489</v>
       </c>
-      <c r="X12" t="s">
-        <v>490</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>492</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>494</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>496</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>498</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>500</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>502</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>629</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>505</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>507</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>508</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>510</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>512</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>514</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>516</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>518</v>
-      </c>
       <c r="AR12" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="AS12" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -39840,7 +39418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CR11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -39934,37 +39512,37 @@
         <v>184</v>
       </c>
       <c r="N1" s="1"/>
-      <c r="O1" s="106" t="s">
+      <c r="O1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
       <c r="S1" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="T1" s="106" t="s">
+      <c r="T1" s="108" t="s">
         <v>141</v>
       </c>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106" t="s">
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
       <c r="AB1" s="19" t="s">
         <v>152</v>
       </c>
       <c r="AC1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="107" t="s">
+      <c r="AD1" s="106" t="s">
         <v>155</v>
       </c>
-      <c r="AE1" s="107"/>
+      <c r="AE1" s="106"/>
       <c r="AF1" s="12" t="s">
         <v>156</v>
       </c>
@@ -39974,18 +39552,18 @@
       <c r="AH1" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AI1" s="107" t="s">
+      <c r="AI1" s="106" t="s">
         <v>161</v>
       </c>
-      <c r="AJ1" s="107"/>
+      <c r="AJ1" s="106"/>
       <c r="AK1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="AL1" s="107" t="s">
+      <c r="AL1" s="106" t="s">
         <v>162</v>
       </c>
-      <c r="AM1" s="107"/>
-      <c r="AN1" s="107"/>
+      <c r="AM1" s="106"/>
+      <c r="AN1" s="106"/>
       <c r="AO1" s="12" t="s">
         <v>85</v>
       </c>
@@ -39995,10 +39573,10 @@
       <c r="AQ1" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="AR1" s="107" t="s">
+      <c r="AR1" s="106" t="s">
         <v>172</v>
       </c>
-      <c r="AS1" s="107"/>
+      <c r="AS1" s="106"/>
       <c r="AT1" s="23" t="s">
         <v>174</v>
       </c>
@@ -40028,56 +39606,56 @@
         <v>184</v>
       </c>
       <c r="BD1" s="24"/>
-      <c r="BE1" s="106" t="s">
+      <c r="BE1" s="108" t="s">
         <v>197</v>
       </c>
-      <c r="BF1" s="106"/>
-      <c r="BG1" s="106"/>
+      <c r="BF1" s="108"/>
+      <c r="BG1" s="108"/>
       <c r="BH1" s="24" t="s">
         <v>186</v>
       </c>
       <c r="BI1" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="BJ1" s="106" t="s">
+      <c r="BJ1" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="BK1" s="106"/>
-      <c r="BL1" s="106"/>
-      <c r="BM1" s="106"/>
-      <c r="BN1" s="106"/>
-      <c r="BO1" s="106"/>
-      <c r="BP1" s="106" t="s">
+      <c r="BK1" s="108"/>
+      <c r="BL1" s="108"/>
+      <c r="BM1" s="108"/>
+      <c r="BN1" s="108"/>
+      <c r="BO1" s="108"/>
+      <c r="BP1" s="108" t="s">
         <v>201</v>
       </c>
-      <c r="BQ1" s="106"/>
+      <c r="BQ1" s="108"/>
       <c r="BR1" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="BS1" s="106" t="s">
+      <c r="BS1" s="108" t="s">
         <v>192</v>
       </c>
-      <c r="BT1" s="106"/>
-      <c r="BU1" s="106"/>
-      <c r="BW1" s="106" t="s">
+      <c r="BT1" s="108"/>
+      <c r="BU1" s="108"/>
+      <c r="BW1" s="108" t="s">
         <v>210</v>
       </c>
-      <c r="BX1" s="106"/>
-      <c r="BY1" s="106"/>
-      <c r="BZ1" s="106"/>
-      <c r="CA1" s="106"/>
-      <c r="CB1" s="106" t="s">
+      <c r="BX1" s="108"/>
+      <c r="BY1" s="108"/>
+      <c r="BZ1" s="108"/>
+      <c r="CA1" s="108"/>
+      <c r="CB1" s="108" t="s">
         <v>213</v>
       </c>
-      <c r="CC1" s="106"/>
-      <c r="CD1" s="106"/>
-      <c r="CE1" s="106"/>
-      <c r="CF1" s="106" t="s">
+      <c r="CC1" s="108"/>
+      <c r="CD1" s="108"/>
+      <c r="CE1" s="108"/>
+      <c r="CF1" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="CG1" s="106"/>
-      <c r="CH1" s="106"/>
-      <c r="CI1" s="106"/>
+      <c r="CG1" s="108"/>
+      <c r="CH1" s="108"/>
+      <c r="CI1" s="108"/>
       <c r="CJ1" s="24" t="s">
         <v>223</v>
       </c>
@@ -40105,7 +39683,7 @@
       </c>
     </row>
     <row r="2" spans="1:96" ht="108.75">
-      <c r="A2" s="108">
+      <c r="A2" s="107">
         <v>2012</v>
       </c>
       <c r="B2" s="16"/>
@@ -40227,7 +39805,7 @@
         <v>190</v>
       </c>
       <c r="BN2" s="4" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="BO2" s="4" t="s">
         <v>199</v>
@@ -40297,7 +39875,7 @@
       <c r="CR2" s="22"/>
     </row>
     <row r="3" spans="1:96">
-      <c r="A3" s="108"/>
+      <c r="A3" s="107"/>
       <c r="E3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -40918,72 +40496,72 @@
         <v>2019</v>
       </c>
       <c r="B10" t="s">
-        <v>698</v>
+        <v>668</v>
       </c>
       <c r="C10" t="s">
-        <v>542</v>
+        <v>513</v>
       </c>
       <c r="D10" t="s">
-        <v>699</v>
+        <v>669</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>541</v>
+        <v>512</v>
       </c>
       <c r="F10" s="21"/>
       <c r="G10" s="29">
         <v>0.3</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="J10" s="100" t="s">
-        <v>549</v>
+        <v>520</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>551</v>
+        <v>522</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>555</v>
+        <v>526</v>
       </c>
       <c r="M10" s="21"/>
       <c r="O10" s="20" t="s">
-        <v>560</v>
+        <v>531</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>563</v>
+        <v>534</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>567</v>
+        <v>538</v>
       </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5" t="s">
         <v>144</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="W10" s="5" t="s">
         <v>144</v>
       </c>
       <c r="Y10" s="22"/>
       <c r="Z10" s="22" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AA10" s="22"/>
       <c r="AB10" s="20" t="s">
-        <v>576</v>
+        <v>547</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="AE10" s="83"/>
       <c r="AF10" s="21" t="s">
@@ -40994,13 +40572,13 @@
         <v>237</v>
       </c>
       <c r="AI10" s="22" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AJ10" s="21" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AK10" s="22" t="s">
-        <v>581</v>
+        <v>552</v>
       </c>
       <c r="AL10" s="22" t="s">
         <v>166</v>
@@ -41012,79 +40590,79 @@
         <v>166</v>
       </c>
       <c r="AO10" s="22" t="s">
-        <v>585</v>
+        <v>556</v>
       </c>
       <c r="AP10" s="4" t="s">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="AQ10" s="22" t="s">
         <v>166</v>
       </c>
       <c r="AR10" s="5" t="s">
-        <v>591</v>
+        <v>562</v>
       </c>
       <c r="AS10" s="7" t="s">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="AT10" s="5" t="s">
-        <v>595</v>
+        <v>566</v>
       </c>
       <c r="AU10" s="5" t="s">
-        <v>597</v>
+        <v>568</v>
       </c>
       <c r="AV10" s="21" t="s">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="AW10" s="5"/>
       <c r="AY10" s="21" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="AZ10" s="21" t="s">
-        <v>606</v>
+        <v>577</v>
       </c>
       <c r="BA10" s="5" t="s">
-        <v>612</v>
+        <v>583</v>
       </c>
       <c r="BB10" s="5" t="s">
-        <v>614</v>
+        <v>585</v>
       </c>
       <c r="BC10" s="21"/>
       <c r="BE10" s="5" t="s">
-        <v>616</v>
+        <v>587</v>
       </c>
       <c r="BF10" s="21" t="s">
-        <v>620</v>
+        <v>591</v>
       </c>
       <c r="BG10" s="21" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="BH10" s="21" t="s">
-        <v>624</v>
+        <v>595</v>
       </c>
       <c r="BI10" s="21" t="s">
-        <v>628</v>
+        <v>599</v>
       </c>
       <c r="BJ10" s="5" t="s">
-        <v>631</v>
+        <v>602</v>
       </c>
       <c r="BK10" s="4" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="BM10" s="20"/>
       <c r="BN10" s="5" t="s">
-        <v>635</v>
+        <v>606</v>
       </c>
       <c r="BO10" s="4" t="s">
-        <v>638</v>
+        <v>609</v>
       </c>
       <c r="BP10" s="20" t="s">
-        <v>640</v>
+        <v>611</v>
       </c>
       <c r="BQ10" s="21" t="s">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="BR10" s="20" t="s">
-        <v>645</v>
+        <v>616</v>
       </c>
       <c r="BS10" s="4" t="s">
         <v>196</v>
@@ -41096,19 +40674,19 @@
         <v>196</v>
       </c>
       <c r="BW10" s="20" t="s">
-        <v>648</v>
+        <v>619</v>
       </c>
       <c r="BX10" s="4" t="s">
-        <v>649</v>
+        <v>620</v>
       </c>
       <c r="BY10" s="20" t="s">
-        <v>651</v>
+        <v>622</v>
       </c>
       <c r="BZ10" s="4" t="s">
-        <v>655</v>
+        <v>626</v>
       </c>
       <c r="CA10" s="5" t="s">
-        <v>656</v>
+        <v>627</v>
       </c>
       <c r="CB10" s="21"/>
       <c r="CC10" s="21"/>
@@ -41117,12 +40695,12 @@
       <c r="CF10" s="5"/>
       <c r="CG10" s="21"/>
       <c r="CH10" s="20" t="s">
-        <v>672</v>
+        <v>643</v>
       </c>
       <c r="CI10" s="21"/>
       <c r="CJ10" s="21"/>
       <c r="CL10" s="1" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="CM10" s="22"/>
       <c r="CN10" s="5" t="s">
@@ -41138,7 +40716,7 @@
         <v>144</v>
       </c>
       <c r="CR10" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:96" ht="96.75">
@@ -41146,106 +40724,106 @@
         <v>2020</v>
       </c>
       <c r="B11" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
       <c r="C11" t="s">
-        <v>697</v>
+        <v>667</v>
       </c>
       <c r="D11" t="s">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="F11" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="G11" s="2">
         <v>0.52149999999999996</v>
       </c>
       <c r="H11" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="I11" t="s">
+        <v>518</v>
+      </c>
+      <c r="J11" t="s">
+        <v>521</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="M11" t="s">
+        <v>528</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="P11" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="S11" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="T11" s="101" t="s">
+        <v>540</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="Y11" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="I11" t="s">
-        <v>547</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="Z11" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="AB11" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>548</v>
+      </c>
+      <c r="AD11" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="M11" t="s">
-        <v>557</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="P11" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="S11" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="T11" s="101" t="s">
-        <v>569</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="Y11" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="Z11" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="AA11" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="AB11" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>577</v>
-      </c>
-      <c r="AD11" s="7" t="s">
-        <v>579</v>
-      </c>
       <c r="AE11" s="83" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="AF11" s="21" t="s">
         <v>236</v>
       </c>
       <c r="AG11" s="7" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="AH11" s="21" t="s">
         <v>237</v>
       </c>
       <c r="AI11" s="22" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AJ11" s="21" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AK11" s="22" t="s">
-        <v>582</v>
+        <v>553</v>
       </c>
       <c r="AL11" s="22" t="s">
         <v>166</v>
@@ -41257,85 +40835,85 @@
         <v>166</v>
       </c>
       <c r="AO11" s="22" t="s">
-        <v>583</v>
+        <v>554</v>
       </c>
       <c r="AP11" s="22" t="s">
-        <v>587</v>
+        <v>558</v>
       </c>
       <c r="AQ11" s="22" t="s">
         <v>166</v>
       </c>
       <c r="AR11" s="5" t="s">
-        <v>590</v>
+        <v>561</v>
       </c>
       <c r="AS11" s="102" t="s">
+        <v>563</v>
+      </c>
+      <c r="AT11" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>569</v>
+      </c>
+      <c r="AV11" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="AW11" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>581</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>579</v>
+      </c>
+      <c r="BA11" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>586</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>528</v>
+      </c>
+      <c r="BE11" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="BF11" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="AT11" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="AU11" t="s">
+      <c r="BG11" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="BH11" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="BI11" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="AV11" s="21" t="s">
-        <v>600</v>
-      </c>
-      <c r="AW11" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>610</v>
-      </c>
-      <c r="AZ11" t="s">
-        <v>608</v>
-      </c>
-      <c r="BA11" s="5" t="s">
+      <c r="BJ11" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="BK11" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="BM11" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="BN11" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="BO11" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="BP11" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="BQ11" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="BB11" t="s">
+      <c r="BR11" s="5" t="s">
         <v>615</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>557</v>
-      </c>
-      <c r="BE11" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="BF11" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="BG11" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="BH11" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="BI11" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="BJ11" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="BK11" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="BM11" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="BN11" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="BO11" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="BP11" s="20" t="s">
-        <v>641</v>
-      </c>
-      <c r="BQ11" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="BR11" s="5" t="s">
-        <v>644</v>
       </c>
       <c r="BS11" s="4" t="s">
         <v>196</v>
@@ -41347,52 +40925,52 @@
         <v>196</v>
       </c>
       <c r="BW11" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="BX11" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="BY11" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="BZ11" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="CA11" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>629</v>
+      </c>
+      <c r="CC11" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="CD11" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="CE11" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="CF11" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="CG11" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="CH11" s="103" t="s">
+        <v>644</v>
+      </c>
+      <c r="CI11" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="BX11" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="BY11" s="20" t="s">
-        <v>653</v>
-      </c>
-      <c r="BZ11" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="CA11" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>658</v>
-      </c>
-      <c r="CC11" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="CD11" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="CE11" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="CF11" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="CG11" s="20" t="s">
-        <v>669</v>
-      </c>
-      <c r="CH11" s="103" t="s">
-        <v>673</v>
-      </c>
-      <c r="CI11" s="5" t="s">
-        <v>675</v>
-      </c>
       <c r="CJ11" s="5" t="s">
-        <v>676</v>
+        <v>647</v>
       </c>
       <c r="CL11" s="1" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="CM11" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="CN11" s="5" t="s">
         <v>144</v>
@@ -41407,11 +40985,18 @@
         <v>144</v>
       </c>
       <c r="CR11" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="BW1:CA1"/>
+    <mergeCell ref="CB1:CE1"/>
+    <mergeCell ref="CF1:CI1"/>
+    <mergeCell ref="BS1:BU1"/>
+    <mergeCell ref="BE1:BG1"/>
+    <mergeCell ref="BJ1:BO1"/>
+    <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="AL1:AN1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="AR1:AS1"/>
@@ -41420,13 +41005,6 @@
     <mergeCell ref="Y1:AA1"/>
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="BW1:CA1"/>
-    <mergeCell ref="CB1:CE1"/>
-    <mergeCell ref="CF1:CI1"/>
-    <mergeCell ref="BS1:BU1"/>
-    <mergeCell ref="BE1:BG1"/>
-    <mergeCell ref="BJ1:BO1"/>
-    <mergeCell ref="BP1:BQ1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41436,7 +41014,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -41520,10 +41098,10 @@
         <v>2020</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -41534,7 +41112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AE18"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -41606,7 +41184,7 @@
       </c>
       <c r="U1" s="109"/>
       <c r="V1" s="39" t="s">
-        <v>702</v>
+        <v>672</v>
       </c>
       <c r="W1" s="11" t="s">
         <v>122</v>
@@ -41614,15 +41192,15 @@
       <c r="X1" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" s="106" t="s">
-        <v>270</v>
-      </c>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
-      <c r="AC1" s="106"/>
-      <c r="AD1" s="106"/>
-      <c r="AE1" s="106"/>
+      <c r="Y1" s="108" t="s">
+        <v>268</v>
+      </c>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
     </row>
     <row r="2" spans="1:31" ht="41.25" customHeight="1">
       <c r="C2" s="1" t="s">
@@ -41658,10 +41236,10 @@
       <c r="O2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="107" t="s">
+      <c r="P2" s="106" t="s">
         <v>118</v>
       </c>
-      <c r="Q2" s="107"/>
+      <c r="Q2" s="106"/>
       <c r="R2" s="1" t="s">
         <v>116</v>
       </c>
@@ -41676,25 +41254,25 @@
       </c>
       <c r="V2" s="4"/>
       <c r="Y2" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AB2" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="AA2" s="4" t="s">
+      <c r="AC2" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AD2" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -41942,53 +41520,54 @@
         <v>2020</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>689</v>
+        <v>659</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>681</v>
+        <v>651</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>683</v>
+        <v>653</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>684</v>
+        <v>654</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>682</v>
+        <v>652</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="J11" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q11" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>690</v>
-      </c>
       <c r="R11" s="9" t="s">
-        <v>694</v>
+        <v>664</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>695</v>
+        <v>665</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>696</v>
+        <v>666</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="AB11" s="1" t="s">
-        <v>278</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:31">
       <c r="J12" s="1"/>
@@ -42019,7 +41598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -42029,7 +41608,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -42051,7 +41630,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="336.75">
@@ -42059,7 +41638,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="296.25">
@@ -42067,7 +41646,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="197.25">
@@ -42075,7 +41654,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="267.75">
@@ -42083,7 +41662,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="363.75" customHeight="1">
@@ -42091,7 +41670,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>704</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
